--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.16898425873574</v>
+        <v>9.939959942044558</v>
       </c>
       <c r="D2" t="n">
-        <v>59.88869118591543</v>
+        <v>9.731912317711258</v>
       </c>
       <c r="E2" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F2" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.67163732887776</v>
+        <v>8.884141065942636</v>
       </c>
       <c r="D3" t="n">
-        <v>53.3425529543951</v>
+        <v>8.668164855089204</v>
       </c>
       <c r="E3" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F3" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.71110180683878</v>
+        <v>10.0280540436113</v>
       </c>
       <c r="D4" t="n">
-        <v>60.74894692125775</v>
+        <v>9.871703874704384</v>
       </c>
       <c r="E4" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F4" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.03951385930853</v>
+        <v>7.481421002137637</v>
       </c>
       <c r="D5" t="n">
-        <v>44.86638181524829</v>
+        <v>7.290787044977847</v>
       </c>
       <c r="E5" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F5" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.90983685901096</v>
+        <v>7.135348489589281</v>
       </c>
       <c r="D6" t="n">
-        <v>42.71856027383808</v>
+        <v>6.941766044498688</v>
       </c>
       <c r="E6" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F6" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.01719795357622</v>
+        <v>4.065294667456136</v>
       </c>
       <c r="D7" t="n">
-        <v>24.31119145318914</v>
+        <v>3.950568611143235</v>
       </c>
       <c r="E7" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F7" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.38905342509288</v>
+        <v>5.588221181577594</v>
       </c>
       <c r="D8" t="n">
-        <v>34.53242352089175</v>
+        <v>5.611518822144911</v>
       </c>
       <c r="E8" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F8" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.85502426983754</v>
+        <v>6.6389414438486</v>
       </c>
       <c r="D9" t="n">
-        <v>40.78195849307241</v>
+        <v>6.627068255124267</v>
       </c>
       <c r="E9" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F9" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.4604788225273</v>
+        <v>3.974827808660687</v>
       </c>
       <c r="D10" t="n">
-        <v>24.96158732824052</v>
+        <v>4.056257940839085</v>
       </c>
       <c r="E10" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F10" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.50416954422071</v>
+        <v>5.444427550935865</v>
       </c>
       <c r="D11" t="n">
-        <v>34.07642406243992</v>
+        <v>5.537418910146487</v>
       </c>
       <c r="E11" t="n">
-        <v>12.88681560216758</v>
+        <v>2.094107535352232</v>
       </c>
       <c r="F11" t="n">
-        <v>12.37797183027471</v>
+        <v>2.01142042241964</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
